--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -34384,12 +34384,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34414,7 +34414,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -34436,68 +34436,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34524,17 +34543,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34559,7 +34578,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -34573,21 +34592,98 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="P196" t="n">
-        <v>0</v>
-      </c>
-      <c r="R196" t="n">
-        <v>0</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -34596,7 +34692,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
@@ -34604,9 +34700,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT196" t="n">
@@ -34614,47 +34715,47 @@
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34681,17 +34782,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34730,168 +34831,76 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="P197" t="n">
-        <v>0</v>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN197" t="b">
-        <v>1</v>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34923,12 +34932,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34953,7 +34962,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -34967,6 +34976,9 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -34975,68 +34987,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35063,7 +35084,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -35098,7 +35119,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -35115,18 +35136,98 @@
       <c r="P199" t="n">
         <v>0</v>
       </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -35220,17 +35321,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35269,168 +35370,76 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="P200" t="n">
-        <v>0</v>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35462,12 +35471,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35492,7 +35501,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -35506,6 +35515,9 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -35514,68 +35526,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35602,7 +35623,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -35637,7 +35658,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -35654,18 +35675,98 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="R202" t="n">
-        <v>0</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -35759,17 +35860,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -35808,168 +35909,76 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36001,12 +36010,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -36031,7 +36040,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -36045,6 +36054,9 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -36053,68 +36065,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36162,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -36176,7 +36197,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36193,18 +36214,98 @@
       <c r="P205" t="n">
         <v>0</v>
       </c>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -36298,17 +36399,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36347,168 +36448,76 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="P206" t="n">
-        <v>0</v>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36540,12 +36549,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36570,12 +36579,12 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N207" t="n">
@@ -36584,6 +36593,9 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -36592,68 +36604,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36680,17 +36701,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -36715,12 +36736,12 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N208" t="n">
@@ -36729,23 +36750,101 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P208" t="n">
+        <v>0</v>
       </c>
       <c r="U208" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_103</t>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -36754,65 +36853,65 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_103</t>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36839,17 +36938,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -36888,165 +36987,76 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO209" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP209" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="AT209" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV209" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37078,12 +37088,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37130,68 +37140,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37218,17 +37242,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37267,17 +37291,34 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -37285,6 +37326,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37292,70 +37391,65 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37382,217 +37476,526 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
+      <c r="AT212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA212" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB212" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC212" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA213" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB213" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC213" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="G214" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>D029</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
         <is>
           <t>白喉</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="K214" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N212" t="n">
-        <v>0</v>
-      </c>
-      <c r="O212" t="n">
-        <v>0</v>
-      </c>
-      <c r="U212" t="inlineStr">
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="U214" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="V212" t="inlineStr">
+      <c r="V214" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="W212" t="inlineStr">
+      <c r="W214" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X212" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>Difteri</t>
         </is>
       </c>
-      <c r="Y212" t="inlineStr">
+      <c r="Y214" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
+      <c r="Z214" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA212" t="inlineStr">
+      <c r="AA214" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB212" t="inlineStr">
+      <c r="AB214" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC212" t="inlineStr">
+      <c r="AC214" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD212" t="inlineStr">
+      <c r="AD214" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE212" t="inlineStr">
+      <c r="AE214" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF212" t="inlineStr">
+      <c r="AF214" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG212" t="inlineStr">
+      <c r="AG214" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH212" t="inlineStr">
+      <c r="AH214" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI212" t="inlineStr">
+      <c r="AI214" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ212" t="inlineStr">
+      <c r="AJ214" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK212" t="inlineStr">
+      <c r="AK214" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM212" t="inlineStr">
+      <c r="AM214" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN212" t="b">
+      <c r="AN214" t="b">
         <v>1</v>
       </c>
-      <c r="AO212" t="inlineStr">
+      <c r="AO214" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP212" t="inlineStr">
+      <c r="AP214" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ212" t="inlineStr">
+      <c r="AQ214" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR212" t="inlineStr">
+      <c r="AR214" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS212" t="inlineStr">
+      <c r="AS214" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="AT212" t="n">
+      <c r="AT214" t="n">
         <v>2</v>
       </c>
-      <c r="AU212" t="inlineStr">
+      <c r="AU214" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV212" t="inlineStr">
+      <c r="AV214" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW212" t="inlineStr">
+      <c r="AW214" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX212" t="inlineStr">
+      <c r="AX214" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY212" t="inlineStr">
+      <c r="AY214" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ212" t="inlineStr">
+      <c r="AZ214" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA212" t="inlineStr">
+      <c r="BA214" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB212" t="inlineStr">
+      <c r="BB214" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC212" t="inlineStr">
+      <c r="BC214" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -37714,7 +38117,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -37724,7 +38127,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -37744,7 +38147,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -32343,13 +32343,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O182" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R182" t="n">
-        <v>0.1616037200588708</v>
+        <v>0.1726221555174302</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -36943,12 +36943,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -36973,12 +36973,12 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N209" t="n">
@@ -37021,42 +37021,42 @@
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37088,12 +37088,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37140,82 +37140,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="AA210" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37242,7 +37228,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -37291,98 +37277,23 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U211" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
-      <c r="V211" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="W211" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X211" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y211" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z211" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB211" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD211" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE211" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF211" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG211" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH211" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI211" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ211" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
-        </is>
-      </c>
-      <c r="AM211" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN211" t="b">
-        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
@@ -37476,17 +37387,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -37525,76 +37436,165 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="R212" t="n">
-        <v>0</v>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
       <c r="AT212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37626,12 +37626,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -37678,87 +37678,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR213" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37785,7 +37766,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -37834,98 +37815,23 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U214" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN214" t="b">
-        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -37996,6 +37902,245 @@
         </is>
       </c>
       <c r="BC214" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N215" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -38117,7 +38262,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -38127,7 +38272,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -38179,7 +38324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -32343,13 +32343,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O182" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R182" t="n">
-        <v>0.1726221555174302</v>
+        <v>0.1799677791564697</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>772</v>
+        <v>774</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -32343,13 +32343,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O182" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R182" t="n">
-        <v>0.1799677791564697</v>
+        <v>0.1836405909759895</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -33443,12 +33443,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33487,6 +33487,9 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
+      <c r="Q190" t="n">
+        <v>0</v>
+      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -33495,82 +33498,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -33597,7 +33586,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -33646,98 +33635,23 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN191" t="b">
-        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -33831,17 +33745,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -33880,76 +33794,165 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
       <c r="AT192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33981,12 +33984,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -34020,100 +34023,81 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R193" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR193" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34140,7 +34124,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -34189,98 +34173,23 @@
       <c r="O194" t="n">
         <v>1</v>
       </c>
+      <c r="R194" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -34379,17 +34288,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34423,22 +34332,39 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
-      </c>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -34446,6 +34372,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -34468,7 +34452,7 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
@@ -34481,42 +34465,42 @@
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34543,7 +34527,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -34592,98 +34576,23 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -34782,17 +34691,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34817,7 +34726,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -34831,76 +34740,170 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="R197" t="n">
-        <v>0</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34932,12 +34935,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34976,9 +34979,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="P198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -34987,77 +34987,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35084,7 +35075,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -35136,98 +35127,18 @@
       <c r="P199" t="n">
         <v>0</v>
       </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R199" t="n">
+        <v>0</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN199" t="b">
-        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -35321,17 +35232,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35356,7 +35267,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -35370,76 +35281,168 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="R200" t="n">
-        <v>0</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN200" t="b">
+        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35471,12 +35474,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35515,9 +35518,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -35526,77 +35526,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35623,7 +35614,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -35675,98 +35666,18 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN202" t="b">
-        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -35860,17 +35771,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -35895,7 +35806,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -35909,76 +35820,168 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36010,12 +36013,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -36054,9 +36057,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="P204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -36065,77 +36065,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36162,7 +36153,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -36214,98 +36205,18 @@
       <c r="P205" t="n">
         <v>0</v>
       </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -36399,17 +36310,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36434,7 +36345,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -36448,76 +36359,168 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="R206" t="n">
-        <v>0</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P206" t="n">
+        <v>0</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36549,12 +36552,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36593,9 +36596,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="P207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -36604,77 +36604,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36701,7 +36692,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -36753,98 +36744,18 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -36938,17 +36849,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -36973,7 +36884,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -36987,76 +36898,168 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37088,12 +37091,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37118,12 +37121,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -37166,42 +37169,42 @@
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37233,12 +37236,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37263,12 +37266,12 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N211" t="n">
@@ -37277,6 +37280,9 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -37285,14 +37291,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -37302,65 +37303,65 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_103</t>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37392,12 +37393,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -37422,12 +37423,12 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N212" t="n">
@@ -37436,19 +37437,22 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
+      <c r="P212" t="n">
+        <v>0</v>
+      </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_103</t>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
         </is>
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_103</t>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
@@ -37463,12 +37467,12 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
@@ -37478,7 +37482,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -37513,12 +37517,12 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
@@ -37536,65 +37540,65 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_103</t>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37626,12 +37630,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -37704,42 +37708,42 @@
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37771,12 +37775,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -37825,7 +37829,7 @@
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -37840,70 +37844,65 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ214" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="AT214" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37935,12 +37934,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -37981,22 +37980,22 @@
       </c>
       <c r="U215" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="V215" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>Difteri</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
@@ -38021,7 +38020,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -38056,17 +38055,17 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -38079,68 +38078,611 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="AT215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
+      <c r="AT216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ215" t="inlineStr">
+      <c r="AQ217" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR215" t="inlineStr">
+      <c r="AR217" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS215" t="inlineStr">
+      <c r="AS217" t="inlineStr">
         <is>
           <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
-      <c r="AT215" t="n">
+      <c r="AT217" t="n">
         <v>2</v>
       </c>
-      <c r="AU215" t="inlineStr">
+      <c r="AU217" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV215" t="inlineStr">
+      <c r="AV217" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW215" t="inlineStr">
+      <c r="AW217" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX215" t="inlineStr">
+      <c r="AX217" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY215" t="inlineStr">
+      <c r="AY217" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ215" t="inlineStr">
+      <c r="AZ217" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA215" t="inlineStr">
+      <c r="BA217" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB215" t="inlineStr">
+      <c r="BB217" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC215" t="inlineStr">
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO218" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -38262,7 +38804,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
@@ -38272,7 +38814,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -38292,7 +38834,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -38324,7 +38866,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -32343,13 +32343,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O182" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R182" t="n">
-        <v>0.1836405909759895</v>
+        <v>0.1909862146150291</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -32343,13 +32343,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O182" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R182" t="n">
-        <v>0.1909862146150291</v>
+        <v>0.1946590264345489</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -32343,13 +32343,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O182" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R182" t="n">
-        <v>0.1946590264345489</v>
+        <v>0.2020046500735885</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -38685,6 +38685,151 @@
       <c r="BC218" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
+      <c r="AT219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA219" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB219" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC219" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38721,7 +38866,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -38804,7 +38949,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10">
@@ -38814,7 +38959,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11">
@@ -38866,7 +39011,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -32343,13 +32343,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O182" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="R182" t="n">
-        <v>0.2020046500735885</v>
+        <v>0.2203687091711874</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -38830,6 +38830,400 @@
       <c r="BC219" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N220" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AT220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA220" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB220" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC220" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU221" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38949,7 +39343,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
@@ -38959,7 +39353,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -38979,7 +39373,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -39011,7 +39405,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>780</v>
+        <v>785</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -32343,13 +32343,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O182" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R182" t="n">
-        <v>0.2203687091711874</v>
+        <v>0.227714332810227</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -33443,12 +33443,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33482,16 +33482,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O190" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>0.0004682466352329422</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -33524,42 +33521,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -33591,12 +33588,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -33635,6 +33632,9 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
+      <c r="Q191" t="n">
+        <v>0</v>
+      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -33643,82 +33643,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -33745,7 +33731,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -33794,98 +33780,23 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -33979,17 +33890,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -34028,76 +33939,165 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="R193" t="n">
-        <v>0</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34129,12 +34129,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -34168,100 +34168,81 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34288,17 +34269,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34332,175 +34313,81 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
-        <v>1</v>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Difteri</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34532,12 +34419,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34571,13 +34458,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -34586,7 +34473,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -34616,7 +34503,7 @@
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT196" t="n">
@@ -34629,42 +34516,42 @@
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34696,12 +34583,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34735,24 +34622,24 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
@@ -34782,7 +34669,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -34817,17 +34704,17 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -34855,7 +34742,7 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT197" t="n">
@@ -34868,42 +34755,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34935,12 +34822,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34965,7 +34852,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -34987,68 +34874,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35075,17 +34981,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35110,7 +35016,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -35124,21 +35030,98 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Difteri</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
@@ -35147,7 +35130,7 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
@@ -35155,9 +35138,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+          <t>SER_SE_FOHM_SMINET_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT199" t="n">
@@ -35165,47 +35153,47 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35232,17 +35220,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35281,168 +35269,76 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="P200" t="n">
-        <v>0</v>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35474,12 +35370,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35504,7 +35400,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -35518,6 +35414,9 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -35526,68 +35425,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35614,7 +35522,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -35649,7 +35557,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -35666,18 +35574,98 @@
       <c r="P202" t="n">
         <v>0</v>
       </c>
-      <c r="R202" t="n">
-        <v>0</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
@@ -35771,17 +35759,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -35820,168 +35808,76 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
-        <v>1</v>
+      <c r="R203" t="n">
+        <v>0</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36013,12 +35909,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -36043,7 +35939,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -36057,6 +35953,9 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -36065,68 +35964,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36153,7 +36061,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -36188,7 +36096,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36205,18 +36113,98 @@
       <c r="P205" t="n">
         <v>0</v>
       </c>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -36310,17 +36298,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36359,168 +36347,76 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="P206" t="n">
-        <v>0</v>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN206" t="b">
-        <v>1</v>
+      <c r="R206" t="n">
+        <v>0</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36552,12 +36448,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36582,7 +36478,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -36596,6 +36492,9 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -36604,68 +36503,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36692,7 +36600,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -36727,7 +36635,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -36744,18 +36652,98 @@
       <c r="P208" t="n">
         <v>0</v>
       </c>
-      <c r="R208" t="n">
-        <v>0</v>
-      </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN208" t="b">
+        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -36849,17 +36837,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -36898,168 +36886,76 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA209" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ209" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37091,12 +36987,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37121,7 +37017,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -37135,6 +37031,9 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -37143,68 +37042,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37231,7 +37139,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -37266,7 +37174,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -37283,18 +37191,98 @@
       <c r="P211" t="n">
         <v>0</v>
       </c>
-      <c r="R211" t="n">
-        <v>0</v>
-      </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN211" t="b">
+        <v>1</v>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
@@ -37388,17 +37376,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -37437,168 +37425,76 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="P212" t="n">
-        <v>0</v>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37630,12 +37526,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -37660,12 +37556,12 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N213" t="n">
@@ -37674,6 +37570,9 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -37682,68 +37581,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37770,17 +37678,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -37805,12 +37713,12 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N214" t="n">
@@ -37819,23 +37727,101 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="R214" t="n">
-        <v>0</v>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P214" t="n">
+        <v>0</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_103</t>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -37844,65 +37830,65 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ214" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_103</t>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
         </is>
       </c>
       <c r="AT214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37929,17 +37915,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -37978,165 +37964,76 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>Diphtheria</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
+      <c r="AT215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
-        </is>
-      </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN215" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP215" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_103</t>
-        </is>
-      </c>
-      <c r="AT215" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV215" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38168,12 +38065,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -38207,13 +38104,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>0.0004682466352329422</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -38246,42 +38143,42 @@
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -38313,12 +38210,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -38367,7 +38264,7 @@
       </c>
       <c r="U217" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -38382,70 +38279,65 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="AT217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38477,12 +38369,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -38523,22 +38415,22 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="V218" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>Difteri</t>
+          <t>Diphtheria</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
@@ -38563,7 +38455,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -38598,17 +38490,17 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN218" t="b">
@@ -38621,70 +38513,65 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_108_MONTHLY</t>
+          <t>SER_FI_THL_TTR_103</t>
         </is>
       </c>
       <c r="AT218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38716,12 +38603,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -38746,7 +38633,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -38794,42 +38681,42 @@
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38861,12 +38748,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -38891,7 +38778,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -38905,9 +38792,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="P220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
@@ -38916,9 +38800,14 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_108_MONTHLY</t>
+        </is>
+      </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -38928,7 +38817,7 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
@@ -38936,9 +38825,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT220" t="n">
@@ -38946,47 +38840,47 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -39018,12 +38912,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -39048,7 +38942,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -39062,27 +38956,24 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="P221" t="n">
-        <v>0</v>
-      </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>Diphtheria</t>
+          <t>Difteri</t>
         </is>
       </c>
       <c r="Y221" t="inlineStr">
@@ -39092,12 +38983,12 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr">
@@ -39107,7 +38998,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -39142,17 +39033,17 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -39165,7 +39056,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
@@ -39173,9 +39064,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR221" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+          <t>SER_NO_FHI_108_MONTHLY</t>
         </is>
       </c>
       <c r="AT221" t="n">
@@ -39183,45 +39079,1123 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV221" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA221" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB221" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC221" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr"/>
+      <c r="AT222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AT223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
           <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
-      <c r="AV221" t="inlineStr">
+      <c r="AV223" t="inlineStr">
         <is>
           <t>cda_weekly_bulletin</t>
         </is>
       </c>
-      <c r="AW221" t="inlineStr">
+      <c r="AW223" t="inlineStr">
         <is>
           <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
-      <c r="AX221" t="inlineStr">
+      <c r="AX223" t="inlineStr">
         <is>
           <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
-      <c r="AY221" t="inlineStr">
+      <c r="AY223" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
       </c>
-      <c r="AZ221" t="inlineStr">
+      <c r="AZ223" t="inlineStr">
         <is>
           <t>cda_weekly_bulletin</t>
         </is>
       </c>
-      <c r="BA221" t="inlineStr">
+      <c r="BA223" t="inlineStr">
         <is>
           <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
-      <c r="BB221" t="inlineStr">
+      <c r="BB223" t="inlineStr">
         <is>
           <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
-      <c r="BC221" t="inlineStr">
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr"/>
+      <c r="AT225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AT227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -39260,7 +40234,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -39343,7 +40317,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10">
@@ -39353,7 +40327,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -39373,7 +40347,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -39405,7 +40379,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -48879,13 +48879,13 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O271" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>0.1248756018636729</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -51118,6 +51118,1083 @@
       <c r="BC283" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr"/>
+      <c r="AT284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AT285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>0</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN286" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_DIPHTHERIA; SER_SG_HIST_DIPHTHERIA</t>
+        </is>
+      </c>
+      <c r="AT286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV286" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA286" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB286" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC286" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="AT287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 103.</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN288" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_103</t>
+        </is>
+      </c>
+      <c r="AT288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>diphtheria</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D029</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Diphtheria</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>白喉</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr"/>
+      <c r="AT289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -51154,7 +52231,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -51237,7 +52314,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -51247,7 +52324,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
@@ -51267,7 +52344,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -51299,7 +52376,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>790</v>
+        <v>824</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -48879,13 +48879,13 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O271" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R271" t="n">
-        <v>0.1248756018636729</v>
+        <v>0.1358940373222322</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d029/2026-2029.xlsx
+++ b/diseases/d029/2026-2029.xlsx
@@ -2533,7 +2533,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -20489,7 +20489,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -29095,7 +29095,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -37682,7 +37682,7 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN208" t="b">
@@ -45634,7 +45634,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -49963,7 +49963,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
